--- a/docs/PROCESS,TASK마이그레이션.xlsx
+++ b/docs/PROCESS,TASK마이그레이션.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CURSOR_DEV\BPMN\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCAC3F4-6D9A-409E-A128-3E532530064F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444D0DBD-EA46-48E0-A92D-A6FE1C54AFB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="1" xr2:uid="{9F896C53-6AC0-4A5C-90B7-7530FADDEDB6}"/>
   </bookViews>
